--- a/resources/templates/standard/M1200-03.xlsx
+++ b/resources/templates/standard/M1200-03.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>주,야 이슈사항 인수인계 일지</t>
   </si>
@@ -640,12 +643,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -680,20 +685,20 @@
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN1" s="4"/>
       <c r="AO1" s="4"/>
       <c r="AP1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ1" s="4"/>
       <c r="AR1" s="4"/>
       <c r="AS1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT1" s="4"/>
       <c r="AU1" s="4"/>
@@ -798,14 +803,14 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -818,7 +823,7 @@
       <c r="O4" s="8"/>
       <c r="P4" s="8"/>
       <c r="Q4" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
@@ -830,7 +835,7 @@
       <c r="Y4" s="8"/>
       <c r="Z4" s="8"/>
       <c r="AA4" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB4" s="9"/>
       <c r="AC4" s="9"/>
@@ -843,7 +848,7 @@
       <c r="AJ4" s="8"/>
       <c r="AK4" s="8"/>
       <c r="AL4" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM4" s="7"/>
       <c r="AN4" s="7"/>
@@ -862,7 +867,7 @@
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
       <c r="F5" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
@@ -875,7 +880,7 @@
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
       <c r="Q5" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R5" s="10"/>
       <c r="S5" s="10"/>
@@ -887,7 +892,7 @@
       <c r="Y5" s="11"/>
       <c r="Z5" s="11"/>
       <c r="AA5" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB5" s="12"/>
       <c r="AC5" s="12"/>
@@ -900,7 +905,7 @@
       <c r="AJ5" s="11"/>
       <c r="AK5" s="11"/>
       <c r="AL5" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM5" s="10"/>
       <c r="AN5" s="10"/>
@@ -919,7 +924,7 @@
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
@@ -942,7 +947,7 @@
       <c r="Y6" s="10"/>
       <c r="Z6" s="10"/>
       <c r="AA6" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB6" s="12"/>
       <c r="AC6" s="12"/>
@@ -967,7 +972,7 @@
     </row>
     <row r="7" ht="68.1" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -1018,7 +1023,7 @@
     </row>
     <row r="8" ht="68.1" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -1069,7 +1074,7 @@
     </row>
     <row r="9" ht="68.1" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -1120,7 +1125,7 @@
     </row>
     <row r="10" ht="68.1" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -1171,7 +1176,7 @@
     </row>
     <row r="11" ht="68.1" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -1222,7 +1227,7 @@
     </row>
     <row r="12" ht="24.95" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
